--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,48 +787,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105310388</v>
+        <v>136712887</v>
       </c>
       <c r="B3" t="n">
-        <v>99140</v>
+        <v>92106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skråmmyrberget, Ång</t>
+          <t>Långåkersjön/Skrämmyrberget, Bergsjön, Yttergundsjö, Själevads s:n, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681106</v>
+        <v>681136</v>
       </c>
       <c r="R3" t="n">
-        <v>7040011</v>
+        <v>7040042</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,12 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,72 +877,83 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105310388</t>
+          <t>https://artportalen.se/Sighting/136712887</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105310387</v>
+        <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>99038</v>
+        <v>92538</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Inner-Bergsjön, Ång</t>
+          <t>Långåkersjön/Skrämmyrberget, Bergsjön, Yttergundsjö, Själevads s:n, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681226</v>
+        <v>681145</v>
       </c>
       <c r="R4" t="n">
-        <v>7039995</v>
+        <v>7040043</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,12 +977,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +991,687 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136712865</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136712813</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långåkersjön/Skrämmyrberget, Bergsjön, Yttergundsjö, Själevads s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>681177</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7040029</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Själevad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136712813</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136713492</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långåkersjön/Skrämmyrberget, Bergsjön, Yttergundsjö, Själevads s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>681150</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7040015</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Själevad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136713492</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136713251</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99263</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långåkersjön/Skrämmyrberget, Bergsjön, Yttergundsjö, Själevads s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>681160</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7040056</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Själevad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136713251</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136713405</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99263</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långåkersjön/Skrämmyrberget, Bergsjön, Yttergundsjö, Själevads s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>681161</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7040078</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Själevad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Monika Norberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136713405</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>105310388</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skråmmyrberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>681106</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7040011</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Själevad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310388</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>105310387</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inner-Bergsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>681226</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7039995</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Själevad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/105310387</t>
         </is>
@@ -1000,6 +1682,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,32 +1015,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136712813</v>
+        <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>92502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,12 +1048,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681177</v>
+        <v>681156</v>
       </c>
       <c r="R5" t="n">
-        <v>7040029</v>
+        <v>7040043</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,6 +1099,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grov granlåga</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1123,13 +1128,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136712813</t>
+          <t>https://artportalen.se/Sighting/136751576</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136713492</v>
+        <v>136712813</v>
       </c>
       <c r="B6" t="n">
         <v>79474</v>
@@ -1159,11 +1164,15 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681150</v>
+        <v>681177</v>
       </c>
       <c r="R6" t="n">
-        <v>7040015</v>
+        <v>7040029</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1233,52 +1242,47 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136713492</t>
+          <t>https://artportalen.se/Sighting/136712813</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136713251</v>
+        <v>136713492</v>
       </c>
       <c r="B7" t="n">
-        <v>99263</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681160</v>
+        <v>681150</v>
       </c>
       <c r="R7" t="n">
-        <v>7040056</v>
+        <v>7040015</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1348,13 +1352,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136713251</t>
+          <t>https://artportalen.se/Sighting/136713492</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136713405</v>
+        <v>136713251</v>
       </c>
       <c r="B8" t="n">
         <v>99263</v>
@@ -1384,7 +1388,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1401,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681161</v>
+        <v>681160</v>
       </c>
       <c r="R8" t="n">
-        <v>7040078</v>
+        <v>7040056</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1463,16 +1467,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136713405</t>
+          <t>https://artportalen.se/Sighting/136713251</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105310388</v>
+        <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99140</v>
+        <v>99263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,37 +1484,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skråmmyrberget, Ång</t>
+          <t>Långåkersjön/Skrämmyrberget, Bergsjön, Yttergundsjö, Själevads s:n, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>681106</v>
+        <v>681161</v>
       </c>
       <c r="R9" t="n">
-        <v>7040011</v>
+        <v>7040078</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,12 +1550,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-06-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,38 +1564,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Tomas Rask</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105310388</t>
+          <t>https://artportalen.se/Sighting/136713405</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105310387</v>
+        <v>105310388</v>
       </c>
       <c r="B10" t="n">
-        <v>99038</v>
+        <v>99140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,30 +1599,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223597</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Inner-Bergsjön, Ång</t>
+          <t>Skråmmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>681226</v>
+        <v>681106</v>
       </c>
       <c r="R10" t="n">
-        <v>7039995</v>
+        <v>7040011</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1672,6 +1688,109 @@
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310388</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>105310387</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inner-Bergsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>681226</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7039995</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Själevad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/105310387</t>
         </is>
@@ -1688,6 +1807,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136712887</v>
       </c>
       <c r="B3" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>92502</v>
+        <v>92507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136712813</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>136713492</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136713251</v>
       </c>
       <c r="B8" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136712887</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>92507</v>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136713251</v>
       </c>
       <c r="B8" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136712887</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>92509</v>
+        <v>92511</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136712813</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>136713492</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136713251</v>
       </c>
       <c r="B8" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136712887</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>92511</v>
+        <v>92513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136712813</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>136713492</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136713251</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136712887</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>92513</v>
+        <v>92514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136712813</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>136713492</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136713251</v>
       </c>
       <c r="B8" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136712887</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>92514</v>
+        <v>92520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136713251</v>
       </c>
       <c r="B8" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136712887</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136712813</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>136713492</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136713251</v>
       </c>
       <c r="B8" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -1361,7 +1361,7 @@
         <v>136713251</v>
       </c>
       <c r="B8" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136712887</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136712813</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>136713492</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136713251</v>
       </c>
       <c r="B8" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136712887</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>92526</v>
+        <v>92539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136712813</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>136713492</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136713251</v>
       </c>
       <c r="B8" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136712887</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136712813</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>136713492</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>136713251</v>
       </c>
       <c r="B8" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -1168,11 +1168,7 @@
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136712887</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>92541</v>
+        <v>92544</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>136713251</v>
       </c>
       <c r="B8" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136712887</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>92544</v>
+        <v>92554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136712813</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>136713492</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>136713251</v>
       </c>
       <c r="B8" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136713405</v>
       </c>
       <c r="B9" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38179-2026 artfynd.xlsx
+++ b/artfynd/A 38179-2026 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136712865</v>
       </c>
       <c r="B4" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136751576</v>
       </c>
       <c r="B5" t="n">
-        <v>92554</v>
+        <v>92555</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
